--- a/data/trans_orig/IP09B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>21664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>41999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>51734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,47 +1224,47 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>11096</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>11278</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>11278</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>41797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>54393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103352</t>
+          <t>103227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>56498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33341</t>
+          <t>33637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>46997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>62916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79100</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>130081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP09B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8722</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3905</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6350</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6331</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,29%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4820</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5431</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7977</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7619</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>58,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5257</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10859</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>59,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13542</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13542</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13542</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9336</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13542</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13542</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28532</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23893</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31840</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19139</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15156</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21664</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15246</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22176</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>80,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28532</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24045</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31874</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41999</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51734</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11248</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4669</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2144</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8652</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8562</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6609</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11096</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35141</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>23808</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>23808</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>23808</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35141</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10914</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7656</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13090</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7398</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10223</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10175</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10914</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7322</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13161</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6301</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9622</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9352</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>13699</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13076</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5310</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7255</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10006</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6635</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13190</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7763</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11085</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5174</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7763</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4579</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11134</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>7874</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>17769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47648</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>61161</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29982</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41303</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29720</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48345</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81807</t>
+          <t>81973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>100480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26582</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20329</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33842</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18966</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13414</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24735</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13882</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24997</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26582</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33145</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>54717</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9654</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5737</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13265</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13391</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11830</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9682</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17126</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10727</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7116</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14644</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6990</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14268</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>52,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13652</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9892</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17267</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -2901,52 +2901,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>21722</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21722</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21722</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>20381</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>20381</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>20381</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21722</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21722</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25942</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20446</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30314</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>22501</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18080</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25119</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18545</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25152</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25942</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>20251</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31026</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41797</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54393</t>
+          <t>54122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12479</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17975</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>5787</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3169</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10208</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9743</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12479</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7395</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38421</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>28288</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12913</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11880</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8253</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15332</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10195</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7055</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12876</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>68,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8319</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4867</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11946</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4808</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11997</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4766</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7906</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>20199</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19332</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9513</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6730</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11991</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11578</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16531</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12545</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19788</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>70,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11559</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3862</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6920</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3663</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10906</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>13375</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53340</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69245</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>46450</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>59996</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45792</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>60211</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52596</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68499</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103227</t>
+          <t>102905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124300</t>
+          <t>124602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>37817</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45215</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28694</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22246</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35792</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22031</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>37817</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30056</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>45959</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>56196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77571</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9487</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3316</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5751</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5720</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3556</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9465</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8865</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6366</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3931</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8174</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8180</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5866</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9682</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16631</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11909</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8548</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15108</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8184</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14662</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13112</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9054</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16732</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>62,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29578</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>7957</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4438</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11925</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>6607</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3854</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10332</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7957</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4337</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12015</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21069</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>18516</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5308,67 +5308,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>4357</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6742</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6912</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4404</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4022</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,01%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3818</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8379</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7625</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6433</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3322</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8805</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3672</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8721</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5038</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8068</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6778</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9626</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4112</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7223</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6778</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3748</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10545</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23419</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35223</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20610</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31256</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20224</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31287</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35233</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22127</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28028</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21107</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15867</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26899</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22127</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16214</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>27687</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6735</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6412</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12558</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9200</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14956</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3790</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8332</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>72,22%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6345</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9703</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5502</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18903</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6966</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11187</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3095</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7111</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29745</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35431</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>23261</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26968</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>79,26%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>63,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>48671</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62916</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9271</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15865</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2378</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10616</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39016</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29346</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53751</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70273</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41701</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53764</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105698</t>
+          <t>94707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130081</t>
+          <t>115901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18598</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15423</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9784</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45930</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56880</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
